--- a/primer_env_data.xlsx
+++ b/primer_env_data.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackb\OneDrive\Desktop\SeedsResearch\Seeds2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{349F51F4-8499-4D40-A58E-2F89E6A7ED16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F0571F7-848F-455C-9E42-C4017C088CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{13D94E65-D451-43E9-8769-B42B33D534F1}"/>
+    <workbookView xWindow="780" yWindow="768" windowWidth="7404" windowHeight="10320" xr2:uid="{13D94E65-D451-43E9-8769-B42B33D534F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -877,6 +878,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BA0696-0198-4140-B94B-95C05E49A7BE}">
   <dimension ref="A1:E121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
